--- a/Unit Testing Generates/ValmontDev/WOD_2__Warranty_Code__c/unitTest_WOD_2__Warranty_Code__c.xlsx
+++ b/Unit Testing Generates/ValmontDev/WOD_2__Warranty_Code__c/unitTest_WOD_2__Warranty_Code__c.xlsx
@@ -2629,7 +2629,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WOD_2__Standard_Labor_Hour__c, WOD_2__Standard_Labor_Minutes__c</t>
+          <t>WOD_2__Standard_Labor_Minutes__c, WOD_2__Standard_Labor_Hour__c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
